--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA142"/>
+  <dimension ref="A1:AA143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15161,6 +15161,99 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Establecimiento de Comercio Vinos y Licores B&amp;B</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Vinos y Licores B&amp;B</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>121861</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Puerto Boyacá</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>14-10 Carrera 4</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>155201</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>https://bybdistribuciones.co</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>comercial@bybdistribuciones.co</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>+57 608 7386088</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr"/>
+      <c r="R143" s="2" t="inlineStr"/>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/byblicores</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/byb_licores</t>
+        </is>
+      </c>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bybdistribuciones</t>
+        </is>
+      </c>
+      <c r="W143" s="2" t="inlineStr"/>
+      <c r="X143" s="2" t="inlineStr"/>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA143"/>
+  <dimension ref="A1:AA144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15254,6 +15254,95 @@
       <c r="Z143" s="2" t="inlineStr"/>
       <c r="AA143" s="2" t="inlineStr"/>
     </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Confiteria El Puma Distribuciones S A S</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Confiteria El Puma Distribuciones S A S</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>108146</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>16 33 Calle 31</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>680006</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://confipuma.com</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>confipuma@gmail.com</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr"/>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>9011235617</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr"/>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Confipuma/</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/confipuma</t>
+        </is>
+      </c>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr"/>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA144"/>
+  <dimension ref="A1:AA145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15343,6 +15343,87 @@
       <c r="Z144" s="2" t="inlineStr"/>
       <c r="AA144" s="2" t="inlineStr"/>
     </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Iliza De Colombia Import &amp; Export S A S</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Iliza De Colombia Import &amp; Export S A S</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>121150</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>San Andrés</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>San Andres and Providencia</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Race 9 #05-48 L-1, Swamp Ground</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>880001</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>https://ilizadecolombia.com</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>ventas@ilizadecolombia.com</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr"/>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr"/>
+      <c r="R145" s="2" t="inlineStr"/>
+      <c r="S145" s="2" t="inlineStr"/>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr">
+        <is>
+          <t>Arlet Puello</t>
+        </is>
+      </c>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Director</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arlet-puello-cardona-07b17220a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA145"/>
+  <dimension ref="A1:AA149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15424,6 +15424,370 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr"/>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr"/>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Ortiz</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Director</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mauricio-ortiz-3a109293</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr"/>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr"/>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Rincon</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/jorge-rincon-38323932</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>108152</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>66-10 Calle 13, Limonar</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>760033</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>info@licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>+57 602 6684493</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="R148" s="2" t="inlineStr"/>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoresjunior</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jrlicoresjunior/</t>
+        </is>
+      </c>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@JRLicoresJunior</t>
+        </is>
+      </c>
+      <c r="W148" s="2" t="inlineStr"/>
+      <c r="X148" s="2" t="inlineStr"/>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>46166</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>67-63 Carrera 6, Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://cava.com.co</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>cavabogota@gmail.com</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr"/>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr"/>
+      <c r="R149" s="2" t="inlineStr"/>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>Valeria Covo</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Partner</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA149"/>
+  <dimension ref="A1:AA153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15788,6 +15788,370 @@
       <c r="Z149" s="2" t="inlineStr"/>
       <c r="AA149" s="2" t="inlineStr"/>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr"/>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Ortiz</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Director</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mauricio-ortiz-3a109293</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr"/>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr"/>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Rincon</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/jorge-rincon-38323932</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>108152</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>66-10 Calle 13, Limonar</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>760033</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>info@licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>+57 602 6684493</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="R152" s="2" t="inlineStr"/>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoresjunior</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jrlicoresjunior/</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@JRLicoresJunior</t>
+        </is>
+      </c>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr"/>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>46166</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>67-63 Carrera 6, Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://cava.com.co</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>cavabogota@gmail.com</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr"/>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr"/>
+      <c r="R153" s="2" t="inlineStr"/>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>Valeria Covo</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Partner</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA153"/>
+  <dimension ref="A1:AA157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16152,6 +16152,370 @@
       <c r="Z153" s="2" t="inlineStr"/>
       <c r="AA153" s="2" t="inlineStr"/>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr"/>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr"/>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Ortiz</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Director</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mauricio-ortiz-3a109293</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr"/>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr"/>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Rincon</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/jorge-rincon-38323932</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>108152</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>66-10 Calle 13, Limonar</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>760033</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>info@licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>+57 602 6684493</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr"/>
+      <c r="R156" s="2" t="inlineStr"/>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoresjunior</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jrlicoresjunior/</t>
+        </is>
+      </c>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@JRLicoresJunior</t>
+        </is>
+      </c>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr"/>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>46166</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>67-63 Carrera 6, Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://cava.com.co</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>cavabogota@gmail.com</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr"/>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr"/>
+      <c r="R157" s="2" t="inlineStr"/>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>Valeria Covo</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Partner</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16516,6 +16516,370 @@
       <c r="Z157" s="2" t="inlineStr"/>
       <c r="AA157" s="2" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Ortiz</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Director</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mauricio-ortiz-3a109293</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr"/>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr"/>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Rincon</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/jorge-rincon-38323932</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>108152</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>66-10 Calle 13, Limonar</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>760033</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>info@licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+57 602 6684493</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr"/>
+      <c r="R160" s="2" t="inlineStr"/>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoresjunior</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jrlicoresjunior/</t>
+        </is>
+      </c>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@JRLicoresJunior</t>
+        </is>
+      </c>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr"/>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>46166</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>67-63 Carrera 6, Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://cava.com.co</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>cavabogota@gmail.com</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr"/>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr"/>
+      <c r="R161" s="2" t="inlineStr"/>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>Valeria Covo</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Partner</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Colombia.xlsx
+++ b/BWI/bestwine_output/bestwine_Colombia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA161"/>
+  <dimension ref="A1:AA165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16880,6 +16880,370 @@
       <c r="Z161" s="2" t="inlineStr"/>
       <c r="AA161" s="2" t="inlineStr"/>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr"/>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>Mauricio Ortiz</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Director</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mauricio-ortiz-3a109293</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Dislicores Store</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Antioquia, El Poblado</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Castropol</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>050021</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dislicores.com</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>online@dislicores.com</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr"/>
+      <c r="P163" s="2" t="inlineStr"/>
+      <c r="Q163" s="2" t="inlineStr"/>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dislicores</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dislicoresstore/</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dislicores</t>
+        </is>
+      </c>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@DislicoresStore</t>
+        </is>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Rincon</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/jorge-rincon-38323932</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Jr Licores Junior</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>108152</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>66-10 Calle 13, Limonar</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>760033</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>info@licoresjunior.com</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>+57 602 6684493</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="R164" s="2" t="inlineStr"/>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/licoresjunior</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jrlicoresjunior/</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@JRLicoresJunior</t>
+        </is>
+      </c>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr"/>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Cava Wine Bar &amp; Shop</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>46166</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>67-63 Carrera 6, Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>110221</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://cava.com.co</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>cavabogota@gmail.com</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr"/>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr"/>
+      <c r="R165" s="2" t="inlineStr"/>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavabarandshop</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>Valeria Covo</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Partner</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
